--- a/public/administrative-personnel-dashboard/personnel-management/DC-3.xlsx
+++ b/public/administrative-personnel-dashboard/personnel-management/DC-3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LGress\Desktop\sicapsystem\public\administrative-personnel-dashboard\personnel-management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792FB366-659A-4A2D-85BD-6298051D53ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBFCDE1-98D9-49A7-9536-FEA4C0F5EA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1755" windowWidth="21600" windowHeight="13845" xr2:uid="{AB36B65C-E162-4FA4-B79E-454E6D20DAD5}"/>
+    <workbookView xWindow="960" yWindow="1692" windowWidth="17280" windowHeight="8964" xr2:uid="{AB36B65C-E162-4FA4-B79E-454E6D20DAD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
   <si>
     <t>FORMATO DC-3</t>
   </si>
@@ -216,9 +216,6 @@
     <t>* Dato no obligatorio</t>
   </si>
   <si>
-    <t xml:space="preserve">SOLEMIR MOISES SANDOVAL ROMERO </t>
-  </si>
-  <si>
     <t>DC-3</t>
   </si>
   <si>
@@ -271,7 +268,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -522,40 +519,75 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -585,43 +617,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -865,6 +862,56 @@
             </a14:hiddenLine>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>15241</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>100895</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>364051</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>22861</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagen 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2B5ABD7-5713-DF95-E4E4-5085431D3135}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="396241" y="5846375"/>
+          <a:ext cx="1834710" cy="668726"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1190,348 +1237,348 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D12C8418-6CA4-44D5-A4DB-87559E87CDB5}">
   <dimension ref="A1:O47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="5.5703125" customWidth="1"/>
-    <col min="5" max="5" width="4.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="5.5546875" customWidth="1"/>
+    <col min="5" max="5" width="4.5546875" customWidth="1"/>
     <col min="6" max="6" width="7" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" customWidth="1"/>
-    <col min="9" max="11" width="6.28515625" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" customWidth="1"/>
-    <col min="13" max="14" width="6.28515625" customWidth="1"/>
-    <col min="15" max="15" width="5.140625" customWidth="1"/>
-    <col min="16" max="16" width="5.85546875" customWidth="1"/>
+    <col min="7" max="7" width="8.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" customWidth="1"/>
+    <col min="9" max="11" width="6.33203125" customWidth="1"/>
+    <col min="12" max="12" width="5.109375" customWidth="1"/>
+    <col min="13" max="14" width="6.33203125" customWidth="1"/>
+    <col min="15" max="15" width="5.109375" customWidth="1"/>
+    <col min="16" max="16" width="5.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:15" ht="69.75" customHeight="1">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="42"/>
-    </row>
-    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="55"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.6">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="39"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="52"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="36"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="49"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="24"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="33"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="46"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="26"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="28"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="22" t="s">
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="24"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="27"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="46"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="40"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="24"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="33"/>
-    </row>
-    <row r="10" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
+      <c r="N8" s="45"/>
+      <c r="O8" s="46"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="26"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="28"/>
+    </row>
+    <row r="10" spans="1:15" ht="8.25" customHeight="1"/>
+    <row r="11" spans="1:15">
+      <c r="A11" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="36"/>
-    </row>
-    <row r="12" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="49"/>
+    </row>
+    <row r="12" spans="1:15" s="3" customFormat="1">
+      <c r="A12" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="24"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
+      <c r="O12" s="46"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="33"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="43" t="s">
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="28"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="44"/>
-      <c r="N14" s="44"/>
-      <c r="O14" s="45"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="31"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="33"/>
-    </row>
-    <row r="16" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="34" t="s">
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="28"/>
+    </row>
+    <row r="16" spans="1:15" ht="8.25" customHeight="1"/>
+    <row r="17" spans="1:15">
+      <c r="A17" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="36"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="48"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="48"/>
+      <c r="O17" s="49"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="24"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
-      <c r="N19" s="29"/>
-      <c r="O19" s="33"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="43" t="s">
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="46"/>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="26"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="28"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="45"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="31"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
         <v>14</v>
@@ -1558,10 +1605,10 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
+    <row r="21" spans="1:15">
+      <c r="A21" s="38"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
       <c r="D21" s="8"/>
       <c r="E21" s="4" t="s">
         <v>15</v>
@@ -1580,408 +1627,377 @@
       <c r="N21" s="18"/>
       <c r="O21" s="19"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="30" t="s">
+    <row r="22" spans="1:15">
+      <c r="A22" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="32"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="27"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="30" t="s">
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="37"/>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="38"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="40"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-      <c r="N24" s="31"/>
-      <c r="O24" s="32"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="29"/>
-      <c r="O25" s="33"/>
-    </row>
-    <row r="26" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="49"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="50"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="51"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="46" t="s">
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="37"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="27"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="28"/>
+    </row>
+    <row r="26" spans="1:15" ht="8.25" customHeight="1"/>
+    <row r="27" spans="1:15" ht="12.75" customHeight="1">
+      <c r="A27" s="41"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="42"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="43"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="48"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="46" t="s">
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="34"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="48"/>
-    </row>
-    <row r="30" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="34"/>
+    </row>
+    <row r="30" spans="1:15" ht="15.75" customHeight="1">
       <c r="A30" s="14"/>
       <c r="O30" s="16"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15">
       <c r="A31" s="14"/>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="F31" s="20" t="s">
+      <c r="C31" s="56"/>
+      <c r="D31" s="56"/>
+      <c r="F31" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="K31" s="20" t="s">
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="56"/>
+      <c r="K31" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="56"/>
+      <c r="N31" s="56"/>
       <c r="O31" s="16"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15">
       <c r="A32" s="14"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="F32" s="53" t="s">
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="F32" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G32" s="53"/>
-      <c r="H32" s="53"/>
-      <c r="I32" s="53"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
       <c r="O32" s="16"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15">
       <c r="A33" s="15"/>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="21" t="s">
+      <c r="F33" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="21" t="s">
+      <c r="K33" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="L33" s="21"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="21"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
       <c r="O33" s="17"/>
     </row>
-    <row r="34" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="8.25" customHeight="1"/>
+    <row r="35" spans="1:15" ht="13.5" customHeight="1">
       <c r="A35" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="9.75" customHeight="1">
+      <c r="A36" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+    </row>
+    <row r="37" spans="1:15" ht="9.75" customHeight="1">
+      <c r="A37" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="20"/>
+    </row>
+    <row r="38" spans="1:15" ht="9.75" customHeight="1">
+      <c r="A38" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="23"/>
+      <c r="L38" s="23"/>
+      <c r="M38" s="23"/>
+      <c r="N38" s="23"/>
+      <c r="O38" s="23"/>
+    </row>
+    <row r="39" spans="1:15" ht="9.75" customHeight="1">
+      <c r="A39" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="23"/>
+      <c r="K39" s="23"/>
+      <c r="L39" s="23"/>
+      <c r="M39" s="23"/>
+      <c r="N39" s="23"/>
+      <c r="O39" s="23"/>
+    </row>
+    <row r="40" spans="1:15" ht="9.75" customHeight="1">
+      <c r="A40" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="23"/>
+      <c r="K40" s="23"/>
+      <c r="L40" s="23"/>
+      <c r="M40" s="23"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="23"/>
+    </row>
+    <row r="41" spans="1:15" ht="9.75" customHeight="1">
+      <c r="A41" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="23"/>
+      <c r="K41" s="23"/>
+      <c r="L41" s="23"/>
+      <c r="M41" s="23"/>
+      <c r="N41" s="23"/>
+      <c r="O41" s="23"/>
+    </row>
+    <row r="42" spans="1:15" ht="8.25" customHeight="1">
+      <c r="A42" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+    </row>
+    <row r="43" spans="1:15" ht="9.75" customHeight="1">
+      <c r="A43" s="23" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="52"/>
-      <c r="K36" s="52"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="52"/>
-    </row>
-    <row r="37" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="52"/>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
-      <c r="H37" s="52"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="52"/>
-      <c r="K37" s="52"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="52"/>
-      <c r="N37" s="52"/>
-      <c r="O37" s="52"/>
-    </row>
-    <row r="38" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="55"/>
-      <c r="C38" s="55"/>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="55"/>
-      <c r="J38" s="55"/>
-      <c r="K38" s="55"/>
-      <c r="L38" s="55"/>
-      <c r="M38" s="55"/>
-      <c r="N38" s="55"/>
-      <c r="O38" s="55"/>
-    </row>
-    <row r="39" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="55"/>
-      <c r="C39" s="55"/>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55"/>
-      <c r="J39" s="55"/>
-      <c r="K39" s="55"/>
-      <c r="L39" s="55"/>
-      <c r="M39" s="55"/>
-      <c r="N39" s="55"/>
-      <c r="O39" s="55"/>
-    </row>
-    <row r="40" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="55" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="55"/>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="55"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="55"/>
-      <c r="N40" s="55"/>
-      <c r="O40" s="55"/>
-    </row>
-    <row r="41" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="55" t="s">
-        <v>33</v>
-      </c>
-      <c r="B41" s="55"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="55"/>
-      <c r="J41" s="55"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="55"/>
-      <c r="M41" s="55"/>
-      <c r="N41" s="55"/>
-      <c r="O41" s="55"/>
-    </row>
-    <row r="42" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="56" t="s">
-        <v>34</v>
-      </c>
-      <c r="B42" s="56"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="56"/>
-      <c r="J42" s="56"/>
-      <c r="K42" s="56"/>
-      <c r="L42" s="56"/>
-      <c r="M42" s="56"/>
-      <c r="N42" s="56"/>
-      <c r="O42" s="56"/>
-    </row>
-    <row r="43" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="55" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="55"/>
-      <c r="C43" s="55"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="55"/>
-      <c r="G43" s="55"/>
-      <c r="H43" s="55"/>
-      <c r="I43" s="55"/>
-      <c r="J43" s="55"/>
-      <c r="K43" s="55"/>
-      <c r="L43" s="55"/>
-      <c r="M43" s="55"/>
-      <c r="N43" s="55"/>
-      <c r="O43" s="55"/>
-    </row>
-    <row r="44" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="23"/>
+      <c r="K43" s="23"/>
+      <c r="L43" s="23"/>
+      <c r="M43" s="23"/>
+      <c r="N43" s="23"/>
+      <c r="O43" s="23"/>
+    </row>
+    <row r="44" spans="1:15" ht="9.75" customHeight="1">
       <c r="A44" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B45" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15">
+      <c r="B45" s="1"/>
+    </row>
+    <row r="46" spans="1:15">
       <c r="N46" s="1"/>
       <c r="O46" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="N47" s="22" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N47" s="54" t="s">
-        <v>38</v>
-      </c>
-      <c r="O47" s="54"/>
+      <c r="O47" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="N47:O47"/>
-    <mergeCell ref="A38:O38"/>
-    <mergeCell ref="A39:O39"/>
-    <mergeCell ref="A40:O40"/>
-    <mergeCell ref="A41:O41"/>
-    <mergeCell ref="A42:O42"/>
-    <mergeCell ref="A43:O43"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="A15:O15"/>
-    <mergeCell ref="A14:O14"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A29:O29"/>
-    <mergeCell ref="A25:O25"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A23:O23"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A19:O19"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A17:O17"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A1:O1"/>
     <mergeCell ref="F31:I31"/>
     <mergeCell ref="F33:I33"/>
     <mergeCell ref="B31:D31"/>
@@ -1998,6 +2014,35 @@
     <mergeCell ref="A13:O13"/>
     <mergeCell ref="A12:O12"/>
     <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="A5:O5"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="A14:O14"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="A38:O38"/>
+    <mergeCell ref="A39:O39"/>
+    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="A42:O42"/>
+    <mergeCell ref="A43:O43"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="B32:D32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/public/administrative-personnel-dashboard/personnel-management/DC-3.xlsx
+++ b/public/administrative-personnel-dashboard/personnel-management/DC-3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LGress\Desktop\sicapsystem\public\administrative-personnel-dashboard\personnel-management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBFCDE1-98D9-49A7-9536-FEA4C0F5EA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138FB725-AAB5-4C71-A005-BA0795DE1C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="1692" windowWidth="17280" windowHeight="8964" xr2:uid="{AB36B65C-E162-4FA4-B79E-454E6D20DAD5}"/>
+    <workbookView xWindow="3855" yWindow="1755" windowWidth="21600" windowHeight="13845" xr2:uid="{AB36B65C-E162-4FA4-B79E-454E6D20DAD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>FORMATO DC-3</t>
   </si>
@@ -263,12 +252,15 @@
   <si>
     <t>SIGERSA INNOVACIONES, S.A. DE C.V. - SIN-120726-TV6-0013</t>
   </si>
+  <si>
+    <t>03.4 INSTALACIÓN Y MANTENIMIENTO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -519,6 +511,96 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -529,96 +611,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1237,348 +1229,350 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D12C8418-6CA4-44D5-A4DB-87559E87CDB5}">
   <dimension ref="A1:O47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="5.5546875" customWidth="1"/>
-    <col min="5" max="5" width="4.5546875" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="5.5703125" customWidth="1"/>
+    <col min="5" max="5" width="4.5703125" customWidth="1"/>
     <col min="6" max="6" width="7" customWidth="1"/>
-    <col min="7" max="7" width="8.109375" customWidth="1"/>
-    <col min="8" max="8" width="5.5546875" customWidth="1"/>
-    <col min="9" max="11" width="6.33203125" customWidth="1"/>
-    <col min="12" max="12" width="5.109375" customWidth="1"/>
-    <col min="13" max="14" width="6.33203125" customWidth="1"/>
-    <col min="15" max="15" width="5.109375" customWidth="1"/>
-    <col min="16" max="16" width="5.88671875" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" customWidth="1"/>
+    <col min="9" max="11" width="6.28515625" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" customWidth="1"/>
+    <col min="13" max="14" width="6.28515625" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" customWidth="1"/>
+    <col min="16" max="16" width="5.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="69.75" customHeight="1">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:15" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="55"/>
-    </row>
-    <row r="2" spans="1:15" ht="15.6">
-      <c r="A2" s="50" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="42"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="52"/>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="47" t="s">
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="39"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="49"/>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="44" t="s">
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="36"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="46"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="26"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="28"/>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="44" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="24"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="28"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="33"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="44" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="46"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="26"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="40"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="44" t="s">
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="24"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="28"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="27"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
-      <c r="N8" s="45"/>
-      <c r="O8" s="46"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="28"/>
-    </row>
-    <row r="10" spans="1:15" ht="8.25" customHeight="1"/>
-    <row r="11" spans="1:15">
-      <c r="A11" s="47" t="s">
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="24"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="28"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="33"/>
+    </row>
+    <row r="10" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="48"/>
-      <c r="M11" s="48"/>
-      <c r="N11" s="48"/>
-      <c r="O11" s="49"/>
-    </row>
-    <row r="12" spans="1:15" s="3" customFormat="1">
-      <c r="A12" s="44" t="s">
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="36"/>
+    </row>
+    <row r="12" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="45"/>
-      <c r="O12" s="46"/>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="26" t="s">
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="24"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="28"/>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="29" t="s">
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="33"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="31"/>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="26" t="s">
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="45"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="27"/>
-      <c r="O15" s="28"/>
-    </row>
-    <row r="16" spans="1:15" ht="8.25" customHeight="1"/>
-    <row r="17" spans="1:15">
-      <c r="A17" s="47" t="s">
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="33"/>
+    </row>
+    <row r="16" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="48"/>
-      <c r="M17" s="48"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="49"/>
-    </row>
-    <row r="18" spans="1:15">
-      <c r="A18" s="44" t="s">
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="36"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="46"/>
-    </row>
-    <row r="19" spans="1:15">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="27"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="27"/>
-      <c r="O19" s="28"/>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="29" t="s">
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="24"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="28"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="33"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="31"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="45"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
         <v>14</v>
@@ -1605,10 +1599,10 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
-      <c r="A21" s="38"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
       <c r="D21" s="8"/>
       <c r="E21" s="4" t="s">
         <v>15</v>
@@ -1627,377 +1621,406 @@
       <c r="N21" s="18"/>
       <c r="O21" s="19"/>
     </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="35" t="s">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="37"/>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="38"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="40"/>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="35" t="s">
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="32"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="25"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="27"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="36"/>
-      <c r="K24" s="36"/>
-      <c r="L24" s="36"/>
-      <c r="M24" s="36"/>
-      <c r="N24" s="36"/>
-      <c r="O24" s="37"/>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="26" t="s">
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="32"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="28"/>
-    </row>
-    <row r="26" spans="1:15" ht="8.25" customHeight="1"/>
-    <row r="27" spans="1:15" ht="12.75" customHeight="1">
-      <c r="A27" s="41"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="42"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="43"/>
-    </row>
-    <row r="28" spans="1:15">
-      <c r="A28" s="32" t="s">
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="33"/>
+    </row>
+    <row r="26" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="49"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="50"/>
+      <c r="M27" s="50"/>
+      <c r="N27" s="50"/>
+      <c r="O27" s="51"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="33"/>
-      <c r="O28" s="34"/>
-    </row>
-    <row r="29" spans="1:15">
-      <c r="A29" s="32" t="s">
+      <c r="B28" s="47"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="47"/>
+      <c r="K28" s="47"/>
+      <c r="L28" s="47"/>
+      <c r="M28" s="47"/>
+      <c r="N28" s="47"/>
+      <c r="O28" s="48"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
-      <c r="O29" s="34"/>
-    </row>
-    <row r="30" spans="1:15" ht="15.75" customHeight="1">
+      <c r="B29" s="47"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="47"/>
+      <c r="M29" s="47"/>
+      <c r="N29" s="47"/>
+      <c r="O29" s="48"/>
+    </row>
+    <row r="30" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
       <c r="O30" s="16"/>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
-      <c r="B31" s="56" t="s">
+      <c r="B31" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="F31" s="56" t="s">
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="F31" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="56"/>
-      <c r="K31" s="56" t="s">
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="K31" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="L31" s="56"/>
-      <c r="M31" s="56"/>
-      <c r="N31" s="56"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
       <c r="O31" s="16"/>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="14"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="F32" s="21" t="s">
+      <c r="B32" s="53"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="F32" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
       <c r="O32" s="16"/>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="15"/>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="25" t="s">
+      <c r="F33" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="25" t="s">
+      <c r="K33" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="L33" s="25"/>
-      <c r="M33" s="25"/>
-      <c r="N33" s="25"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="21"/>
       <c r="O33" s="17"/>
     </row>
-    <row r="34" spans="1:15" ht="8.25" customHeight="1"/>
-    <row r="35" spans="1:15" ht="13.5" customHeight="1">
+    <row r="34" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="9.75" customHeight="1">
-      <c r="A36" s="20" t="s">
+    <row r="36" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="20"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="20"/>
-      <c r="L36" s="20"/>
-      <c r="M36" s="20"/>
-      <c r="N36" s="20"/>
-      <c r="O36" s="20"/>
-    </row>
-    <row r="37" spans="1:15" ht="9.75" customHeight="1">
-      <c r="A37" s="20" t="s">
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="52"/>
+      <c r="K36" s="52"/>
+      <c r="L36" s="52"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="52"/>
+      <c r="O36" s="52"/>
+    </row>
+    <row r="37" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="20"/>
-    </row>
-    <row r="38" spans="1:15" ht="9.75" customHeight="1">
-      <c r="A38" s="23" t="s">
+      <c r="B37" s="52"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="52"/>
+      <c r="K37" s="52"/>
+      <c r="L37" s="52"/>
+      <c r="M37" s="52"/>
+      <c r="N37" s="52"/>
+      <c r="O37" s="52"/>
+    </row>
+    <row r="38" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="23"/>
-      <c r="K38" s="23"/>
-      <c r="L38" s="23"/>
-      <c r="M38" s="23"/>
-      <c r="N38" s="23"/>
-      <c r="O38" s="23"/>
-    </row>
-    <row r="39" spans="1:15" ht="9.75" customHeight="1">
-      <c r="A39" s="23" t="s">
+      <c r="B38" s="55"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="55"/>
+      <c r="J38" s="55"/>
+      <c r="K38" s="55"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="55"/>
+      <c r="N38" s="55"/>
+      <c r="O38" s="55"/>
+    </row>
+    <row r="39" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
-      <c r="J39" s="23"/>
-      <c r="K39" s="23"/>
-      <c r="L39" s="23"/>
-      <c r="M39" s="23"/>
-      <c r="N39" s="23"/>
-      <c r="O39" s="23"/>
-    </row>
-    <row r="40" spans="1:15" ht="9.75" customHeight="1">
-      <c r="A40" s="23" t="s">
+      <c r="B39" s="55"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="55"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="55"/>
+      <c r="N39" s="55"/>
+      <c r="O39" s="55"/>
+    </row>
+    <row r="40" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="23"/>
-      <c r="M40" s="23"/>
-      <c r="N40" s="23"/>
-      <c r="O40" s="23"/>
-    </row>
-    <row r="41" spans="1:15" ht="9.75" customHeight="1">
-      <c r="A41" s="23" t="s">
+      <c r="B40" s="55"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="55"/>
+      <c r="K40" s="55"/>
+      <c r="L40" s="55"/>
+      <c r="M40" s="55"/>
+      <c r="N40" s="55"/>
+      <c r="O40" s="55"/>
+    </row>
+    <row r="41" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
-      <c r="J41" s="23"/>
-      <c r="K41" s="23"/>
-      <c r="L41" s="23"/>
-      <c r="M41" s="23"/>
-      <c r="N41" s="23"/>
-      <c r="O41" s="23"/>
-    </row>
-    <row r="42" spans="1:15" ht="8.25" customHeight="1">
-      <c r="A42" s="24" t="s">
+      <c r="B41" s="55"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="55"/>
+      <c r="J41" s="55"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="55"/>
+      <c r="N41" s="55"/>
+      <c r="O41" s="55"/>
+    </row>
+    <row r="42" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-    </row>
-    <row r="43" spans="1:15" ht="9.75" customHeight="1">
-      <c r="A43" s="23" t="s">
+      <c r="B42" s="56"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="56"/>
+      <c r="K42" s="56"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="56"/>
+      <c r="N42" s="56"/>
+      <c r="O42" s="56"/>
+    </row>
+    <row r="43" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="23"/>
-      <c r="K43" s="23"/>
-      <c r="L43" s="23"/>
-      <c r="M43" s="23"/>
-      <c r="N43" s="23"/>
-      <c r="O43" s="23"/>
-    </row>
-    <row r="44" spans="1:15" ht="9.75" customHeight="1">
+      <c r="B43" s="55"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="55"/>
+      <c r="K43" s="55"/>
+      <c r="L43" s="55"/>
+      <c r="M43" s="55"/>
+      <c r="N43" s="55"/>
+      <c r="O43" s="55"/>
+    </row>
+    <row r="44" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B45" s="1"/>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="N46" s="1"/>
       <c r="O46" s="12" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
-      <c r="N47" s="22" t="s">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N47" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="O47" s="22"/>
+      <c r="O47" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="A38:O38"/>
+    <mergeCell ref="A39:O39"/>
+    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="A42:O42"/>
+    <mergeCell ref="A43:O43"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="A14:O14"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="A5:O5"/>
+    <mergeCell ref="A1:O1"/>
     <mergeCell ref="F31:I31"/>
     <mergeCell ref="F33:I33"/>
     <mergeCell ref="B31:D31"/>
@@ -2014,35 +2037,6 @@
     <mergeCell ref="A13:O13"/>
     <mergeCell ref="A12:O12"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A15:O15"/>
-    <mergeCell ref="A14:O14"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A29:O29"/>
-    <mergeCell ref="A25:O25"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A23:O23"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A19:O19"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A17:O17"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="N47:O47"/>
-    <mergeCell ref="A38:O38"/>
-    <mergeCell ref="A39:O39"/>
-    <mergeCell ref="A40:O40"/>
-    <mergeCell ref="A41:O41"/>
-    <mergeCell ref="A42:O42"/>
-    <mergeCell ref="A43:O43"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="B32:D32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/public/administrative-personnel-dashboard/personnel-management/DC-3.xlsx
+++ b/public/administrative-personnel-dashboard/personnel-management/DC-3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LGress\Desktop\sicapsystem\public\administrative-personnel-dashboard\personnel-management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138FB725-AAB5-4C71-A005-BA0795DE1C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2CCCA3-2534-4D2D-AB6E-0A90E47B0D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="1755" windowWidth="21600" windowHeight="13845" xr2:uid="{AB36B65C-E162-4FA4-B79E-454E6D20DAD5}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="13845" xr2:uid="{AB36B65C-E162-4FA4-B79E-454E6D20DAD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
   <si>
     <t>FORMATO DC-3</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>03.4 INSTALACIÓN Y MANTENIMIENTO</t>
+  </si>
+  <si>
+    <t>6000- SEGURIDAD</t>
   </si>
 </sst>
 </file>
@@ -511,40 +514,75 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -574,43 +612,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1247,332 +1250,332 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="42"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="55"/>
     </row>
     <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="39"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="52"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="36"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="49"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="24"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="46"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="33"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="28"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="22" t="s">
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="24"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="46"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="25" t="s">
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="27"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="40"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="24"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
+      <c r="N8" s="45"/>
+      <c r="O8" s="46"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="33"/>
+      <c r="A9" s="26"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="28"/>
     </row>
     <row r="10" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="36"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="49"/>
     </row>
     <row r="12" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="24"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
+      <c r="O12" s="46"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="33"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="28"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="44"/>
-      <c r="N14" s="44"/>
-      <c r="O14" s="45"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="31"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="33"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="28"/>
     </row>
     <row r="16" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="36"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="48"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="48"/>
+      <c r="O17" s="49"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="24"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="46"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
-      <c r="N19" s="29"/>
-      <c r="O19" s="33"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="28"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="43" t="s">
+      <c r="A20" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="45"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="31"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
         <v>14</v>
@@ -1600,9 +1603,9 @@
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
       <c r="D21" s="8"/>
       <c r="E21" s="4" t="s">
         <v>15</v>
@@ -1622,134 +1625,136 @@
       <c r="O21" s="19"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="32"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="37"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="27"/>
+      <c r="A23" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="40"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-      <c r="N24" s="31"/>
-      <c r="O24" s="32"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="37"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="29"/>
-      <c r="O25" s="33"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="27"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="28"/>
     </row>
     <row r="26" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="49"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="50"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="51"/>
+      <c r="A27" s="41"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="42"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="43"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="46" t="s">
+      <c r="A28" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="48"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="34"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="46" t="s">
+      <c r="A29" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="48"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="34"/>
     </row>
     <row r="30" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
@@ -1757,59 +1762,59 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="F31" s="20" t="s">
+      <c r="C31" s="56"/>
+      <c r="D31" s="56"/>
+      <c r="F31" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="K31" s="20" t="s">
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="56"/>
+      <c r="K31" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="56"/>
+      <c r="N31" s="56"/>
       <c r="O31" s="16"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="14"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="F32" s="53" t="s">
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="F32" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G32" s="53"/>
-      <c r="H32" s="53"/>
-      <c r="I32" s="53"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
       <c r="O32" s="16"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="15"/>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="21" t="s">
+      <c r="F33" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="21" t="s">
+      <c r="K33" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="L33" s="21"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="21"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
       <c r="O33" s="17"/>
     </row>
     <row r="34" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1819,156 +1824,156 @@
       </c>
     </row>
     <row r="36" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="52" t="s">
+      <c r="A36" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="52"/>
-      <c r="K36" s="52"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="52"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
     </row>
     <row r="37" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="52" t="s">
+      <c r="A37" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="52"/>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
-      <c r="H37" s="52"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="52"/>
-      <c r="K37" s="52"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="52"/>
-      <c r="N37" s="52"/>
-      <c r="O37" s="52"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="20"/>
     </row>
     <row r="38" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="55" t="s">
+      <c r="A38" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="55"/>
-      <c r="C38" s="55"/>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="55"/>
-      <c r="J38" s="55"/>
-      <c r="K38" s="55"/>
-      <c r="L38" s="55"/>
-      <c r="M38" s="55"/>
-      <c r="N38" s="55"/>
-      <c r="O38" s="55"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="23"/>
+      <c r="L38" s="23"/>
+      <c r="M38" s="23"/>
+      <c r="N38" s="23"/>
+      <c r="O38" s="23"/>
     </row>
     <row r="39" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="55" t="s">
+      <c r="A39" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="55"/>
-      <c r="C39" s="55"/>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55"/>
-      <c r="J39" s="55"/>
-      <c r="K39" s="55"/>
-      <c r="L39" s="55"/>
-      <c r="M39" s="55"/>
-      <c r="N39" s="55"/>
-      <c r="O39" s="55"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="23"/>
+      <c r="K39" s="23"/>
+      <c r="L39" s="23"/>
+      <c r="M39" s="23"/>
+      <c r="N39" s="23"/>
+      <c r="O39" s="23"/>
     </row>
     <row r="40" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="55" t="s">
+      <c r="A40" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="55"/>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="55"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="55"/>
-      <c r="N40" s="55"/>
-      <c r="O40" s="55"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="23"/>
+      <c r="K40" s="23"/>
+      <c r="L40" s="23"/>
+      <c r="M40" s="23"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="23"/>
     </row>
     <row r="41" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="55" t="s">
+      <c r="A41" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B41" s="55"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="55"/>
-      <c r="J41" s="55"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="55"/>
-      <c r="M41" s="55"/>
-      <c r="N41" s="55"/>
-      <c r="O41" s="55"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="23"/>
+      <c r="K41" s="23"/>
+      <c r="L41" s="23"/>
+      <c r="M41" s="23"/>
+      <c r="N41" s="23"/>
+      <c r="O41" s="23"/>
     </row>
     <row r="42" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="56" t="s">
+      <c r="A42" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="B42" s="56"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="56"/>
-      <c r="J42" s="56"/>
-      <c r="K42" s="56"/>
-      <c r="L42" s="56"/>
-      <c r="M42" s="56"/>
-      <c r="N42" s="56"/>
-      <c r="O42" s="56"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
     </row>
     <row r="43" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="55" t="s">
+      <c r="A43" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="55"/>
-      <c r="C43" s="55"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="55"/>
-      <c r="G43" s="55"/>
-      <c r="H43" s="55"/>
-      <c r="I43" s="55"/>
-      <c r="J43" s="55"/>
-      <c r="K43" s="55"/>
-      <c r="L43" s="55"/>
-      <c r="M43" s="55"/>
-      <c r="N43" s="55"/>
-      <c r="O43" s="55"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="23"/>
+      <c r="K43" s="23"/>
+      <c r="L43" s="23"/>
+      <c r="M43" s="23"/>
+      <c r="N43" s="23"/>
+      <c r="O43" s="23"/>
     </row>
     <row r="44" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
@@ -1985,42 +1990,13 @@
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N47" s="54" t="s">
+      <c r="N47" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="O47" s="54"/>
+      <c r="O47" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="N47:O47"/>
-    <mergeCell ref="A38:O38"/>
-    <mergeCell ref="A39:O39"/>
-    <mergeCell ref="A40:O40"/>
-    <mergeCell ref="A41:O41"/>
-    <mergeCell ref="A42:O42"/>
-    <mergeCell ref="A43:O43"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="A15:O15"/>
-    <mergeCell ref="A14:O14"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A29:O29"/>
-    <mergeCell ref="A25:O25"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A23:O23"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A19:O19"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A17:O17"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A1:O1"/>
     <mergeCell ref="F31:I31"/>
     <mergeCell ref="F33:I33"/>
     <mergeCell ref="B31:D31"/>
@@ -2037,6 +2013,35 @@
     <mergeCell ref="A13:O13"/>
     <mergeCell ref="A12:O12"/>
     <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="A5:O5"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="A14:O14"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="A38:O38"/>
+    <mergeCell ref="A39:O39"/>
+    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="A42:O42"/>
+    <mergeCell ref="A43:O43"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="B32:D32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
